--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.92996363305652</v>
+        <v>8.926119090371685</v>
       </c>
       <c r="D2" t="n">
-        <v>13.15770617937921</v>
+        <v>2.138127254149122</v>
       </c>
       <c r="E2" t="n">
-        <v>10.77746894268401</v>
+        <v>1.751338703186152</v>
       </c>
       <c r="F2" t="n">
-        <v>6.064668045679583</v>
+        <v>0.9855085574229322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.67674305573566</v>
+        <v>7.584970746557046</v>
       </c>
       <c r="D3" t="n">
-        <v>28.54297193996331</v>
+        <v>4.638232940244038</v>
       </c>
       <c r="E3" t="n">
-        <v>10.77746894268401</v>
+        <v>1.751338703186152</v>
       </c>
       <c r="F3" t="n">
-        <v>6.064668045679583</v>
+        <v>0.9855085574229322</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.0456138627941</v>
+        <v>4.232412252704042</v>
       </c>
       <c r="D4" t="n">
-        <v>26.0473020983977</v>
+        <v>4.232686590989627</v>
       </c>
       <c r="E4" t="n">
-        <v>10.77746894268401</v>
+        <v>1.751338703186152</v>
       </c>
       <c r="F4" t="n">
-        <v>6.064668045679583</v>
+        <v>0.9855085574229322</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.22976143635456</v>
+        <v>5.399836233407616</v>
       </c>
       <c r="D5" t="n">
-        <v>33.48346849397085</v>
+        <v>5.441063630270262</v>
       </c>
       <c r="E5" t="n">
-        <v>10.77746894268401</v>
+        <v>1.751338703186152</v>
       </c>
       <c r="F5" t="n">
-        <v>6.064668045679583</v>
+        <v>0.9855085574229322</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.39716751249852</v>
+        <v>3.96453972078101</v>
       </c>
       <c r="D6" t="n">
-        <v>24.41301158248593</v>
+        <v>3.967114382153963</v>
       </c>
       <c r="E6" t="n">
-        <v>10.77746894268401</v>
+        <v>1.751338703186152</v>
       </c>
       <c r="F6" t="n">
-        <v>6.064668045679583</v>
+        <v>0.9855085574229322</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.75991580728386</v>
+        <v>7.110986318683628</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24870945828754</v>
+        <v>4.915415286971726</v>
       </c>
       <c r="E7" t="n">
-        <v>10.77746894268401</v>
+        <v>1.751338703186152</v>
       </c>
       <c r="F7" t="n">
-        <v>6.064668045679583</v>
+        <v>0.9855085574229322</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.3009750729568</v>
+        <v>4.76140844935548</v>
       </c>
       <c r="D8" t="n">
-        <v>29.31091608658345</v>
+        <v>4.763023864069812</v>
       </c>
       <c r="E8" t="n">
-        <v>10.77746894268401</v>
+        <v>1.751338703186152</v>
       </c>
       <c r="F8" t="n">
-        <v>6.064668045679583</v>
+        <v>0.9855085574229322</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
